--- a/file_upload_forms/036_stand_up_comedy_night_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/036_stand_up_comedy_night_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Performer Info</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>review_submission</t>
+          <t>review_submission_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Review Submission</t>
+          <t>Review Submission 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_submission</t>
+          <t>event_submission_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event Submission</t>
+          <t>Event Submission 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>Submit Button</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Performer Info</t>
+          <t>String 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
